--- a/Unibots-London Tracker.xlsx
+++ b/Unibots-London Tracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nanayawasarefrimpong/Library/Mobile Documents/com~apple~CloudDocs/Desktop/Uni/Year 4/ME/Robotics Society/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nanayawasarefrimpong/Library/Mobile Documents/com~apple~CloudDocs/Desktop/Uni/Year 4/ME/Robotics Society/Unibots-London/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A2EB2C-A859-5243-9DC8-4560D06ADA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105F23C9-B1F0-B547-9880-F72B612C3CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16320" xr2:uid="{B1D9FD05-6417-8046-9372-C419A8EF7527}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Item</t>
   </si>
@@ -81,9 +81,6 @@
     <t>Ball Collection</t>
   </si>
   <si>
-    <t>Limit switches (detect when platform reaches top)</t>
-  </si>
-  <si>
     <t>360 Servo//DC Motor</t>
   </si>
   <si>
@@ -93,12 +90,6 @@
     <t>Qty</t>
   </si>
   <si>
-    <t>Buck converter IC to power raspberry pi</t>
-  </si>
-  <si>
-    <t>Buck/LDO IC for sensors</t>
-  </si>
-  <si>
     <t>Headers</t>
   </si>
   <si>
@@ -117,7 +108,31 @@
     <t>Motor Driver IC</t>
   </si>
   <si>
-    <t>ToF (Time of Flight)  sensors</t>
+    <t>ToF (Time of Flight)  sensor (for parking)</t>
+  </si>
+  <si>
+    <t>https://amzn.eu/d/010pBdcB</t>
+  </si>
+  <si>
+    <t>Limit switches (parking &amp; detect when platform reaches top)</t>
+  </si>
+  <si>
+    <t>https://amzn.eu/d/09tM5Ntx</t>
+  </si>
+  <si>
+    <t>https://amzn.eu/d/08Unudxx</t>
+  </si>
+  <si>
+    <t>5V Buck converter IC to power raspberry pi, esp32 &amp;sensors</t>
+  </si>
+  <si>
+    <t>5V Redundant LDO IC for sensors and esp32 if needed</t>
+  </si>
+  <si>
+    <t>LM1117</t>
+  </si>
+  <si>
+    <t>AP64502Q (tried before)</t>
   </si>
 </sst>
 </file>
@@ -497,99 +512,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FDE024E-5D18-0147-A12C-9F3E555DCB24}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -597,7 +625,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -605,30 +633,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>14</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>15</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -648,16 +682,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
